--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97542</v>
+        <v>97550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97550</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127492606</v>
       </c>
       <c r="B2" t="n">
-        <v>97552</v>
+        <v>97553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127492606</v>
+        <v>119039651</v>
       </c>
       <c r="B2" t="n">
-        <v>97553</v>
+        <v>104132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>1910</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästberg mot NO, Hl</t>
+          <t>Hästberg  mot O, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373428</v>
+        <v>373514</v>
       </c>
       <c r="R2" t="n">
-        <v>6312122</v>
+        <v>6312179</v>
       </c>
       <c r="S2" t="n">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>+ flerstädes mot N</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsväg dike</t>
+          <t>Skogsväg grus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -783,6 +788,348 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127495964</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104132</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hästberg mot NO, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>373491</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6312130</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Slättåkra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogsväg grus</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112253884</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bohults vindkraftpark i NO2, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>373239</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6312223</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Slättåkra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Skogsvägkant fukt</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127492606</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästberg mot NO, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>373428</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6312122</v>
+      </c>
+      <c r="S5" t="n">
+        <v>106</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Slättåkra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsväg dike</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127495964</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127492606</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,8 +1265,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134950151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37137-2025 artfynd.xlsx
+++ b/artfynd/A 37137-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>134950151</v>
       </c>
       <c r="B6" t="n">
-        <v>98271</v>
+        <v>98315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
